--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$174</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5947" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5981" uniqueCount="663">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1031,8 +1031,22 @@
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this.resolve()}
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn:tumorkonferenz</t>
+  </si>
+  <si>
+    <t>tumorkonferenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-tumorkonferenz)
+</t>
   </si>
   <si>
     <t>Procedure.partOf</t>
@@ -2382,7 +2396,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL173"/>
+  <dimension ref="A1:AL174"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.1015625" customWidth="true" bestFit="true"/>
@@ -8364,7 +8378,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>321</v>
       </c>
@@ -8439,16 +8453,14 @@
         <v>75</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>321</v>
@@ -8463,7 +8475,7 @@
         <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -8474,21 +8486,23 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>86</v>
@@ -8500,16 +8514,16 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8559,7 +8573,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8571,7 +8585,7 @@
         <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -8582,42 +8596,42 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>75</v>
+        <v>333</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>334</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>10</v>
+        <v>335</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8643,13 +8657,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>337</v>
+        <v>75</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>338</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -8667,19 +8681,19 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -8688,44 +8702,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>340</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>341</v>
+        <v>10</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8751,13 +8765,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8775,10 +8789,10 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>85</v>
@@ -8796,16 +8810,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>75</v>
+        <v>344</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8815,7 +8829,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -8827,13 +8841,13 @@
         <v>214</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8862,10 +8876,10 @@
         <v>151</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8883,7 +8897,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8904,12 +8918,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8923,24 +8937,26 @@
         <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>101</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8965,13 +8981,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>75</v>
+        <v>355</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8989,7 +9005,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8998,10 +9014,10 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
@@ -9012,21 +9028,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -9038,17 +9054,15 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -9085,31 +9099,31 @@
         <v>75</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
@@ -9120,14 +9134,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9143,23 +9157,21 @@
         <v>75</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9195,9 +9207,11 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9205,7 +9219,7 @@
         <v>112</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9217,7 +9231,7 @@
         <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -9226,16 +9240,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
@@ -9244,10 +9256,10 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>75</v>
@@ -9259,10 +9271,10 @@
         <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>358</v>
+        <v>226</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>228</v>
@@ -9278,7 +9290,7 @@
         <v>75</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>75</v>
@@ -9293,26 +9305,26 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>361</v>
+        <v>75</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>230</v>
@@ -9336,14 +9348,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
@@ -9355,25 +9369,29 @@
         <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>101</v>
+        <v>362</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
       </c>
@@ -9382,7 +9400,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -9397,13 +9415,11 @@
         <v>75</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>75</v>
+        <v>365</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -9421,19 +9437,19 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
@@ -9444,21 +9460,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>75</v>
@@ -9470,17 +9486,15 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9517,31 +9531,31 @@
         <v>75</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
@@ -9550,48 +9564,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
       </c>
@@ -9627,31 +9639,31 @@
         <v>75</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
@@ -9660,12 +9672,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9673,13 +9685,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -9688,18 +9700,20 @@
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
       </c>
@@ -9747,7 +9761,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9768,12 +9782,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9781,13 +9795,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>75</v>
@@ -9796,20 +9810,18 @@
         <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
       </c>
@@ -9857,7 +9869,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9878,12 +9890,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9891,13 +9903,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
@@ -9906,19 +9918,19 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9967,7 +9979,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9990,10 +10002,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10016,19 +10028,19 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10077,7 +10089,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10100,10 +10112,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10126,19 +10138,19 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10187,7 +10199,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10208,26 +10220,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>379</v>
+        <v>75</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
@@ -10236,19 +10248,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>380</v>
+        <v>272</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>381</v>
+        <v>273</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>349</v>
+        <v>274</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>382</v>
+        <v>275</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -10273,13 +10285,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>383</v>
+        <v>75</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>384</v>
+        <v>75</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -10297,7 +10309,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>378</v>
+        <v>276</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10309,7 +10321,7 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>385</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
@@ -10318,44 +10330,48 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>75</v>
+        <v>383</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>101</v>
+        <v>384</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -10379,13 +10395,13 @@
         <v>75</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>75</v>
+        <v>387</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>75</v>
+        <v>388</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -10403,7 +10419,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>103</v>
+        <v>382</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10412,10 +10428,10 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>75</v>
+        <v>389</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
@@ -10426,21 +10442,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
@@ -10452,17 +10468,15 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10499,31 +10513,31 @@
         <v>75</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
@@ -10534,46 +10548,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>75</v>
       </c>
@@ -10582,7 +10594,7 @@
         <v>75</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>389</v>
+        <v>75</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>75</v>
@@ -10609,9 +10621,11 @@
         <v>75</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>75</v>
       </c>
@@ -10619,7 +10633,7 @@
         <v>112</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10631,7 +10645,7 @@
         <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
@@ -10640,25 +10654,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>86</v>
@@ -10670,16 +10682,16 @@
         <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>392</v>
+        <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>393</v>
+        <v>226</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>394</v>
+        <v>227</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>395</v>
+        <v>228</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>229</v>
@@ -10692,7 +10704,7 @@
         <v>75</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>75</v>
@@ -10707,26 +10719,26 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>397</v>
+        <v>75</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>230</v>
@@ -10750,14 +10762,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
@@ -10769,25 +10783,29 @@
         <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>100</v>
+        <v>396</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>101</v>
+        <v>397</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>75</v>
       </c>
@@ -10796,7 +10814,7 @@
         <v>75</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>75</v>
@@ -10811,13 +10829,11 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>75</v>
+        <v>401</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -10835,19 +10851,19 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>75</v>
@@ -10858,21 +10874,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>75</v>
@@ -10884,17 +10900,15 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -10931,31 +10945,31 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
@@ -10964,16 +10978,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>105</v>
       </c>
@@ -10982,10 +10994,10 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
@@ -10994,13 +11006,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>406</v>
+        <v>108</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>109</v>
@@ -11041,16 +11053,16 @@
         <v>75</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>113</v>
@@ -11076,18 +11088,20 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="B81" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>85</v>
@@ -11099,29 +11113,27 @@
         <v>75</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>127</v>
+        <v>408</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>409</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>238</v>
+        <v>410</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>410</v>
+        <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -11163,19 +11175,19 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>75</v>
@@ -11212,24 +11224,26 @@
         <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>413</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>414</v>
+        <v>238</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>75</v>
+        <v>414</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>75</v>
@@ -11271,7 +11285,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11289,15 +11303,15 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>415</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11320,20 +11334,18 @@
         <v>86</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="N83" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
       </c>
@@ -11345,7 +11357,7 @@
         <v>75</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>419</v>
+        <v>75</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>75</v>
@@ -11381,7 +11393,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11393,21 +11405,21 @@
         <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL83" t="s" s="2">
+      <c r="B84" t="s" s="2">
         <v>421</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11415,13 +11427,13 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>75</v>
@@ -11430,19 +11442,19 @@
         <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>258</v>
+        <v>422</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11455,7 +11467,7 @@
         <v>75</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>75</v>
+        <v>423</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>75</v>
@@ -11491,7 +11503,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11503,21 +11515,21 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>98</v>
+        <v>424</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>75</v>
+        <v>425</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11540,19 +11552,19 @@
         <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -11601,7 +11613,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11622,16 +11634,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
@@ -11643,7 +11653,7 @@
         <v>85</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>75</v>
@@ -11652,19 +11662,19 @@
         <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>358</v>
+        <v>265</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>359</v>
+        <v>266</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -11674,7 +11684,7 @@
         <v>75</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>75</v>
@@ -11689,11 +11699,13 @@
         <v>75</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>427</v>
+        <v>75</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -11711,13 +11723,13 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>97</v>
@@ -11732,14 +11744,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
@@ -11751,25 +11765,29 @@
         <v>85</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>101</v>
+        <v>362</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
@@ -11778,7 +11796,7 @@
         <v>75</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>75</v>
@@ -11793,13 +11811,11 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>75</v>
+        <v>431</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -11817,19 +11833,19 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
@@ -11840,21 +11856,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>75</v>
@@ -11866,17 +11882,15 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11913,31 +11927,31 @@
         <v>75</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>75</v>
@@ -11946,48 +11960,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
       </c>
@@ -12023,31 +12035,31 @@
         <v>75</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
@@ -12056,9 +12068,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>412</v>
@@ -12069,13 +12081,13 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>75</v>
@@ -12084,18 +12096,20 @@
         <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>75</v>
       </c>
@@ -12143,7 +12157,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12164,12 +12178,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12177,13 +12191,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>75</v>
@@ -12192,20 +12206,18 @@
         <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
       </c>
@@ -12253,7 +12265,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12274,12 +12286,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12287,13 +12299,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>75</v>
@@ -12302,19 +12314,19 @@
         <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12363,7 +12375,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12386,10 +12398,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12412,19 +12424,19 @@
         <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>75</v>
@@ -12473,7 +12485,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12496,10 +12508,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12522,19 +12534,19 @@
         <v>86</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -12583,7 +12595,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12604,26 +12616,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>75</v>
@@ -12632,18 +12644,20 @@
         <v>86</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>438</v>
+        <v>100</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>439</v>
+        <v>272</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>440</v>
+        <v>273</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
       </c>
@@ -12691,10 +12705,10 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>436</v>
+        <v>276</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>85</v>
@@ -12703,7 +12717,7 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
@@ -12714,18 +12728,18 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>75</v>
+        <v>441</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>85</v>
@@ -12749,7 +12763,7 @@
         <v>444</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>445</v>
+        <v>326</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12799,10 +12813,10 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>85</v>
@@ -12811,7 +12825,7 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
@@ -12820,12 +12834,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12833,7 +12847,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>85</v>
@@ -12848,16 +12862,16 @@
         <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12895,17 +12909,19 @@
         <v>75</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AC97" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>452</v>
+        <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12917,7 +12933,7 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
@@ -12926,16 +12942,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
@@ -12956,16 +12970,16 @@
         <v>86</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13003,19 +13017,17 @@
         <v>75</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>75</v>
+        <v>456</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13030,34 +13042,34 @@
         <v>98</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
         <v>457</v>
       </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
+      <c r="B99" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>75</v>
@@ -13066,16 +13078,16 @@
         <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L99" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="N99" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13125,7 +13137,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13140,20 +13152,22 @@
         <v>98</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>75</v>
+        <v>461</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="B100" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
@@ -13183,7 +13197,7 @@
         <v>466</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>326</v>
+        <v>454</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13233,7 +13247,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13245,7 +13259,7 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -13282,13 +13296,13 @@
         <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>326</v>
@@ -13353,7 +13367,7 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
@@ -13364,10 +13378,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13378,7 +13392,7 @@
         <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>75</v>
@@ -13390,7 +13404,7 @@
         <v>86</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>472</v>
@@ -13398,7 +13412,9 @@
       <c r="M102" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N102" s="2"/>
+      <c r="N102" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -13447,19 +13463,19 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -13484,7 +13500,7 @@
         <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>75</v>
@@ -13493,16 +13509,16 @@
         <v>75</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>100</v>
+        <v>475</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>101</v>
+        <v>476</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>102</v>
+        <v>477</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13553,19 +13569,19 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>103</v>
+        <v>474</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
@@ -13576,21 +13592,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>75</v>
@@ -13602,17 +13618,15 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -13649,31 +13663,31 @@
         <v>75</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
@@ -13684,14 +13698,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>477</v>
+        <v>105</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13704,26 +13718,24 @@
         <v>75</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>478</v>
+        <v>107</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>479</v>
+        <v>108</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="O105" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>75</v>
       </c>
@@ -13759,19 +13771,19 @@
         <v>75</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>480</v>
+        <v>113</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -13794,33 +13806,33 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>75</v>
+        <v>481</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>482</v>
@@ -13829,10 +13841,10 @@
         <v>483</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>484</v>
+        <v>304</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>75</v>
@@ -13857,13 +13869,13 @@
         <v>75</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>485</v>
+        <v>75</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>486</v>
+        <v>75</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>75</v>
@@ -13881,19 +13893,19 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>75</v>
@@ -13904,10 +13916,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13915,7 +13927,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>85</v>
@@ -13930,19 +13942,19 @@
         <v>86</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>75</v>
@@ -13967,13 +13979,13 @@
         <v>75</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>75</v>
+        <v>489</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>75</v>
+        <v>490</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -13991,10 +14003,10 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>85</v>
@@ -14003,7 +14015,7 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
@@ -14014,10 +14026,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14025,7 +14037,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>85</v>
@@ -14037,22 +14049,22 @@
         <v>75</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>326</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -14101,10 +14113,10 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>85</v>
@@ -14113,7 +14125,7 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
@@ -14124,10 +14136,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14147,22 +14159,22 @@
         <v>75</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>326</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -14211,7 +14223,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14223,7 +14235,7 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
@@ -14234,10 +14246,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14248,7 +14260,7 @@
         <v>76</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>75</v>
@@ -14260,7 +14272,7 @@
         <v>86</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>214</v>
+        <v>502</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>503</v>
@@ -14269,9 +14281,11 @@
         <v>504</v>
       </c>
       <c r="N110" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>75</v>
       </c>
@@ -14295,13 +14309,13 @@
         <v>75</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>506</v>
+        <v>75</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>507</v>
+        <v>75</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -14319,19 +14333,19 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
@@ -14340,12 +14354,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14359,7 +14373,7 @@
         <v>77</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>75</v>
@@ -14368,16 +14382,16 @@
         <v>86</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14403,13 +14417,13 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>75</v>
+        <v>510</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>511</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -14427,7 +14441,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14439,7 +14453,7 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
@@ -14450,10 +14464,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14476,7 +14490,7 @@
         <v>86</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>214</v>
+        <v>513</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>514</v>
@@ -14511,13 +14525,13 @@
         <v>75</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>517</v>
+        <v>75</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>518</v>
+        <v>75</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -14535,7 +14549,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14547,7 +14561,7 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>75</v>
@@ -14556,12 +14570,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14572,27 +14586,29 @@
         <v>76</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>101</v>
+        <v>518</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -14617,13 +14633,13 @@
         <v>75</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>75</v>
+        <v>521</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>75</v>
+        <v>522</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -14641,19 +14657,19 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>103</v>
+        <v>517</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>75</v>
@@ -14664,21 +14680,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>75</v>
@@ -14690,17 +14706,15 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -14737,31 +14751,31 @@
         <v>75</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>75</v>
@@ -14772,14 +14786,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14789,29 +14803,27 @@
         <v>77</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
       </c>
@@ -14847,9 +14859,11 @@
         <v>75</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AC115" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD115" t="s" s="2">
         <v>75</v>
       </c>
@@ -14857,7 +14871,7 @@
         <v>112</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14869,7 +14883,7 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
@@ -14878,16 +14892,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
@@ -14896,7 +14908,7 @@
         <v>76</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>86</v>
@@ -14911,10 +14923,10 @@
         <v>139</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>358</v>
+        <v>226</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>228</v>
@@ -14957,16 +14969,14 @@
         <v>75</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF116" t="s" s="2">
         <v>230</v>
@@ -14990,14 +15000,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="B117" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C117" s="2"/>
+      <c r="C117" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15009,25 +15021,29 @@
         <v>85</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>101</v>
+        <v>362</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15075,19 +15091,19 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
@@ -15098,21 +15114,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>75</v>
@@ -15124,17 +15140,15 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -15171,31 +15185,31 @@
         <v>75</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
@@ -15204,48 +15218,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>75</v>
       </c>
@@ -15254,7 +15266,7 @@
         <v>75</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>531</v>
+        <v>75</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>75</v>
@@ -15281,31 +15293,31 @@
         <v>75</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>75</v>
@@ -15316,10 +15328,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15327,7 +15339,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>85</v>
@@ -15342,18 +15354,20 @@
         <v>86</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>75</v>
       </c>
@@ -15362,7 +15376,7 @@
         <v>75</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>75</v>
+        <v>535</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>75</v>
@@ -15401,7 +15415,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -15424,10 +15438,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15435,7 +15449,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>85</v>
@@ -15450,20 +15464,18 @@
         <v>86</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>75</v>
       </c>
@@ -15511,7 +15523,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15532,12 +15544,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15545,13 +15557,13 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
@@ -15560,19 +15572,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>75</v>
@@ -15621,7 +15633,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -15644,10 +15656,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15670,19 +15682,19 @@
         <v>86</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -15731,7 +15743,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -15754,10 +15766,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15780,19 +15792,19 @@
         <v>86</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>75</v>
@@ -15841,7 +15853,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15862,12 +15874,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15881,7 +15893,7 @@
         <v>85</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
@@ -15890,18 +15902,20 @@
         <v>86</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>542</v>
+        <v>272</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>543</v>
+        <v>273</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -15925,11 +15939,13 @@
         <v>75</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>545</v>
+        <v>75</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
@@ -15947,7 +15963,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>541</v>
+        <v>276</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15965,15 +15981,15 @@
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>546</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15987,24 +16003,26 @@
         <v>85</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>101</v>
+        <v>546</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>75</v>
@@ -16029,13 +16047,11 @@
         <v>75</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>75</v>
+        <v>549</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>75</v>
@@ -16053,7 +16069,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>103</v>
+        <v>545</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16062,35 +16078,35 @@
         <v>85</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>75</v>
+        <v>550</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>75</v>
@@ -16102,17 +16118,15 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>75</v>
@@ -16149,31 +16163,31 @@
         <v>75</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
@@ -16184,14 +16198,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16207,23 +16221,21 @@
         <v>75</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>550</v>
+        <v>107</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>551</v>
+        <v>108</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>75</v>
       </c>
@@ -16259,19 +16271,19 @@
         <v>75</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16283,7 +16295,7 @@
         <v>75</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>75</v>
@@ -16294,10 +16306,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16308,7 +16320,7 @@
         <v>76</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>75</v>
@@ -16317,19 +16329,23 @@
         <v>75</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>101</v>
+        <v>554</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>75</v>
       </c>
@@ -16377,19 +16393,19 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
@@ -16400,21 +16416,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>75</v>
@@ -16426,17 +16442,15 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>75</v>
@@ -16473,31 +16487,31 @@
         <v>75</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>75</v>
@@ -16506,48 +16520,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>75</v>
       </c>
@@ -16556,7 +16568,7 @@
         <v>75</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>555</v>
+        <v>75</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>75</v>
@@ -16583,31 +16595,31 @@
         <v>75</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>75</v>
@@ -16616,12 +16628,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16635,7 +16647,7 @@
         <v>85</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>75</v>
@@ -16644,18 +16656,20 @@
         <v>86</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>75</v>
       </c>
@@ -16664,7 +16678,7 @@
         <v>75</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>75</v>
+        <v>559</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>75</v>
@@ -16703,7 +16717,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -16724,12 +16738,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16743,7 +16757,7 @@
         <v>85</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>75</v>
@@ -16752,18 +16766,18 @@
         <v>86</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>75</v>
       </c>
@@ -16811,7 +16825,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -16832,12 +16846,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16851,7 +16865,7 @@
         <v>85</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>75</v>
@@ -16860,17 +16874,17 @@
         <v>86</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -16919,7 +16933,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -16942,10 +16956,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16968,19 +16982,17 @@
         <v>86</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>75</v>
@@ -17029,7 +17041,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17052,10 +17064,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17078,19 +17090,19 @@
         <v>86</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>75</v>
@@ -17139,7 +17151,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17162,10 +17174,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17176,7 +17188,7 @@
         <v>76</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>75</v>
@@ -17185,21 +17197,23 @@
         <v>75</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>562</v>
+        <v>100</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>563</v>
+        <v>272</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>564</v>
+        <v>273</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>75</v>
       </c>
@@ -17247,19 +17261,19 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>561</v>
+        <v>276</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>75</v>
@@ -17270,10 +17284,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17287,7 +17301,7 @@
         <v>77</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>75</v>
@@ -17296,7 +17310,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>214</v>
+        <v>566</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>567</v>
@@ -17331,29 +17345,31 @@
         <v>75</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>570</v>
+        <v>75</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>571</v>
+        <v>75</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC138" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -17365,25 +17381,23 @@
         <v>97</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>572</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>574</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>75</v>
       </c>
@@ -17407,13 +17421,13 @@
         <v>214</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -17439,9 +17453,11 @@
         <v>75</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y139" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="Z139" t="s" s="2">
         <v>575</v>
       </c>
@@ -17449,19 +17465,17 @@
         <v>75</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17479,17 +17493,19 @@
         <v>75</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>75</v>
+        <v>576</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>75</v>
       </c>
@@ -17498,10 +17514,10 @@
         <v>76</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>75</v>
@@ -17510,15 +17526,17 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>101</v>
+        <v>571</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>75</v>
@@ -17543,13 +17561,11 @@
         <v>75</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>75</v>
+        <v>579</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>75</v>
@@ -17567,19 +17583,19 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>103</v>
+        <v>570</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>75</v>
@@ -17590,21 +17606,21 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>75</v>
@@ -17616,17 +17632,15 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>75</v>
@@ -17663,31 +17677,31 @@
         <v>75</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>75</v>
@@ -17698,14 +17712,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -17721,23 +17735,21 @@
         <v>75</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>582</v>
+        <v>107</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>583</v>
+        <v>108</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>75</v>
       </c>
@@ -17773,19 +17785,19 @@
         <v>75</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -17797,7 +17809,7 @@
         <v>75</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>75</v>
@@ -17822,7 +17834,7 @@
         <v>76</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>75</v>
@@ -17831,19 +17843,23 @@
         <v>75</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>101</v>
+        <v>586</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>75</v>
       </c>
@@ -17891,19 +17907,19 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>75</v>
@@ -17914,21 +17930,21 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>75</v>
@@ -17940,17 +17956,15 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>75</v>
@@ -17987,31 +18001,31 @@
         <v>75</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>75</v>
@@ -18022,21 +18036,21 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>75</v>
@@ -18045,23 +18059,21 @@
         <v>75</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>75</v>
       </c>
@@ -18070,7 +18082,7 @@
         <v>75</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>590</v>
+        <v>75</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>75</v>
@@ -18097,31 +18109,31 @@
         <v>75</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>75</v>
@@ -18132,10 +18144,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18158,18 +18170,20 @@
         <v>86</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>75</v>
       </c>
@@ -18178,7 +18192,7 @@
         <v>75</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>75</v>
+        <v>594</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>75</v>
@@ -18217,7 +18231,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -18238,12 +18252,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18251,13 +18265,13 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>75</v>
@@ -18266,18 +18280,18 @@
         <v>86</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>75</v>
       </c>
@@ -18325,7 +18339,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -18346,12 +18360,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18359,13 +18373,13 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>75</v>
@@ -18374,17 +18388,17 @@
         <v>86</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>75</v>
@@ -18433,7 +18447,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -18456,10 +18470,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18482,19 +18496,17 @@
         <v>86</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>75</v>
@@ -18543,7 +18555,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -18566,10 +18578,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18592,19 +18604,19 @@
         <v>86</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>75</v>
@@ -18653,7 +18665,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -18674,16 +18686,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>75</v>
       </c>
@@ -18692,30 +18702,32 @@
         <v>76</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J151" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K151" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>567</v>
+        <v>272</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>568</v>
+        <v>273</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="O151" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>75</v>
       </c>
@@ -18739,11 +18751,13 @@
         <v>75</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y151" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z151" t="s" s="2">
-        <v>603</v>
+        <v>75</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>75</v>
@@ -18761,16 +18775,16 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>566</v>
+        <v>276</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>98</v>
@@ -18782,14 +18796,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C152" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="D152" t="s" s="2">
         <v>75</v>
       </c>
@@ -18798,10 +18814,10 @@
         <v>76</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>75</v>
@@ -18810,15 +18826,17 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>101</v>
+        <v>571</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>75</v>
@@ -18843,13 +18861,11 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>75</v>
+        <v>607</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
@@ -18867,19 +18883,19 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>103</v>
+        <v>570</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>75</v>
@@ -18890,21 +18906,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>75</v>
@@ -18916,17 +18932,15 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>75</v>
@@ -18963,31 +18977,31 @@
         <v>75</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>75</v>
@@ -18998,14 +19012,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -19021,23 +19035,21 @@
         <v>75</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>607</v>
+        <v>107</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>608</v>
+        <v>108</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>75</v>
       </c>
@@ -19073,19 +19085,19 @@
         <v>75</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19097,7 +19109,7 @@
         <v>75</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>75</v>
@@ -19108,7 +19120,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>585</v>
@@ -19122,7 +19134,7 @@
         <v>76</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>75</v>
@@ -19131,19 +19143,23 @@
         <v>75</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>101</v>
+        <v>611</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>75</v>
       </c>
@@ -19191,19 +19207,19 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>75</v>
@@ -19214,21 +19230,21 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>75</v>
@@ -19240,17 +19256,15 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>75</v>
@@ -19287,31 +19301,31 @@
         <v>75</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>75</v>
@@ -19322,21 +19336,21 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>75</v>
@@ -19345,23 +19359,21 @@
         <v>75</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>75</v>
       </c>
@@ -19370,7 +19382,7 @@
         <v>75</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>612</v>
+        <v>75</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>75</v>
@@ -19397,31 +19409,31 @@
         <v>75</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>75</v>
@@ -19432,10 +19444,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19443,7 +19455,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>85</v>
@@ -19458,18 +19470,20 @@
         <v>86</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>75</v>
       </c>
@@ -19478,7 +19492,7 @@
         <v>75</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>75</v>
+        <v>616</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>75</v>
@@ -19517,7 +19531,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -19540,10 +19554,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19551,7 +19565,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>85</v>
@@ -19566,18 +19580,18 @@
         <v>86</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>75</v>
       </c>
@@ -19625,7 +19639,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -19648,10 +19662,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19659,7 +19673,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>85</v>
@@ -19674,17 +19688,17 @@
         <v>86</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>75</v>
@@ -19733,7 +19747,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -19756,10 +19770,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19782,19 +19796,17 @@
         <v>86</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>75</v>
@@ -19843,7 +19855,7 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -19866,10 +19878,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19892,19 +19904,19 @@
         <v>86</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>75</v>
@@ -19953,7 +19965,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -19976,10 +19988,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19990,7 +20002,7 @@
         <v>76</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>75</v>
@@ -19999,22 +20011,22 @@
         <v>75</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>619</v>
+        <v>100</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>620</v>
+        <v>272</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>621</v>
+        <v>273</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>326</v>
+        <v>274</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>622</v>
+        <v>275</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>75</v>
@@ -20063,19 +20075,19 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>618</v>
+        <v>276</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>75</v>
@@ -20086,10 +20098,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20112,7 +20124,7 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>214</v>
+        <v>623</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>624</v>
@@ -20121,9 +20133,11 @@
         <v>625</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>75</v>
       </c>
@@ -20147,13 +20161,13 @@
         <v>75</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>626</v>
+        <v>75</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>627</v>
+        <v>75</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>75</v>
@@ -20171,7 +20185,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -20183,7 +20197,7 @@
         <v>97</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>75</v>
@@ -20192,12 +20206,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20211,7 +20225,7 @@
         <v>77</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>75</v>
@@ -20220,16 +20234,16 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L165" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="N165" t="s" s="2">
-        <v>632</v>
+        <v>353</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -20255,13 +20269,13 @@
         <v>75</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>75</v>
+        <v>630</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>75</v>
+        <v>631</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>75</v>
@@ -20279,7 +20293,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -20300,12 +20314,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20319,7 +20333,7 @@
         <v>77</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>75</v>
@@ -20328,7 +20342,7 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>471</v>
+        <v>633</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>634</v>
@@ -20336,7 +20350,9 @@
       <c r="M166" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N166" s="2"/>
+      <c r="N166" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>75</v>
@@ -20385,7 +20401,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -20408,10 +20424,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20422,7 +20438,7 @@
         <v>76</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>75</v>
@@ -20434,13 +20450,13 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>100</v>
+        <v>475</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>101</v>
+        <v>638</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>102</v>
+        <v>639</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20491,19 +20507,19 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>103</v>
+        <v>637</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>75</v>
@@ -20514,21 +20530,21 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>75</v>
@@ -20540,17 +20556,15 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>75</v>
@@ -20587,31 +20601,31 @@
         <v>75</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>75</v>
@@ -20622,14 +20636,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>477</v>
+        <v>105</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -20642,26 +20656,24 @@
         <v>75</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>478</v>
+        <v>107</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>479</v>
+        <v>108</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="O169" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>75</v>
       </c>
@@ -20697,19 +20709,19 @@
         <v>75</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>480</v>
+        <v>113</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -20732,44 +20744,46 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>75</v>
+        <v>481</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I170" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>640</v>
+        <v>482</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>641</v>
+        <v>483</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O170" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>75</v>
       </c>
@@ -20793,13 +20807,13 @@
         <v>75</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>642</v>
+        <v>75</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>643</v>
+        <v>75</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>75</v>
@@ -20817,19 +20831,19 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>639</v>
+        <v>484</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>75</v>
@@ -20840,10 +20854,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20851,7 +20865,7 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G171" t="s" s="2">
         <v>85</v>
@@ -20866,16 +20880,16 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="L171" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="N171" t="s" s="2">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20901,13 +20915,13 @@
         <v>75</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>75</v>
+        <v>646</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>75</v>
+        <v>647</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>75</v>
@@ -20925,10 +20939,10 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>85</v>
@@ -20937,7 +20951,7 @@
         <v>97</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>75</v>
@@ -20959,10 +20973,10 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>75</v>
@@ -20983,11 +20997,9 @@
         <v>651</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>653</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>75</v>
       </c>
@@ -21038,16 +21050,16 @@
         <v>648</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>75</v>
@@ -21058,10 +21070,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21084,18 +21096,20 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>214</v>
+        <v>653</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="N173" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O173" s="2"/>
+      <c r="O173" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>75</v>
       </c>
@@ -21119,13 +21133,13 @@
         <v>75</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>657</v>
+        <v>75</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>658</v>
+        <v>75</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>75</v>
@@ -21143,7 +21157,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -21155,17 +21169,125 @@
         <v>97</v>
       </c>
       <c r="AJ173" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O174" s="2"/>
+      <c r="P174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AK173" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL173" t="s" s="2">
+      <c r="AK174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL174" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL173">
+  <autoFilter ref="A1:AL174">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21175,7 +21297,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI172">
+  <conditionalFormatting sqref="A2:AI173">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5981" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5980" uniqueCount="663">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1297,10 +1297,10 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>Seitenlokalisation (OPS-Seitenzusatz R/L/B)</t>
+  </si>
+  <si>
+    <t>Seitenangabe bei paarigen Organen und OPS-Codes mit Seitenzusatzpflicht über die Basisprofil-Extension seitenlokalisation (R/L/B). Das oBDS sieht am OP kein eigenes Seitenfeld vor; führend ist der OPS-Seitenzusatz.</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.system</t>
@@ -11097,7 +11097,7 @@
         <v>407</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11124,9 +11124,7 @@
       <c r="M81" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="N81" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$213</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7871" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7912" uniqueCount="789">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1495,6 +1495,9 @@
     <t>Procedure.code.coding.extension.value[x].code</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
   </si>
   <si>
@@ -2024,6 +2027,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2760,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO212"/>
+  <dimension ref="A1:AO213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -5120,7 +5139,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -5352,7 +5371,7 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -13877,7 +13896,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>117</v>
@@ -14226,7 +14245,7 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>117</v>
@@ -14456,7 +14475,7 @@
         <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>101</v>
@@ -14688,7 +14707,7 @@
         <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>117</v>
@@ -14807,7 +14826,7 @@
         <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>101</v>
@@ -14924,7 +14943,7 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>101</v>
@@ -14981,7 +15000,9 @@
       <c r="M105" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N105" s="2"/>
+      <c r="N105" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O105" t="s" s="2">
         <v>248</v>
       </c>
@@ -15041,7 +15062,7 @@
         <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>101</v>
@@ -15064,10 +15085,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15098,7 +15119,9 @@
       <c r="M106" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N106" s="2"/>
+      <c r="N106" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>255</v>
       </c>
@@ -15158,7 +15181,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
@@ -15181,10 +15204,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15277,7 +15300,7 @@
         <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>101</v>
@@ -15300,10 +15323,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15329,7 +15352,7 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>231</v>
@@ -15345,7 +15368,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -15396,7 +15419,7 @@
         <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>101</v>
@@ -15419,10 +15442,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15448,10 +15471,10 @@
         <v>103</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>241</v>
@@ -15513,7 +15536,7 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
@@ -15522,7 +15545,7 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -15536,10 +15559,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15565,12 +15588,14 @@
         <v>164</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N110" s="2"/>
+      <c r="N110" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O110" t="s" s="2">
         <v>248</v>
       </c>
@@ -15585,7 +15610,7 @@
         <v>78</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>78</v>
@@ -15630,16 +15655,16 @@
         <v>89</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -15653,10 +15678,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15687,7 +15712,9 @@
       <c r="M111" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N111" s="2"/>
+      <c r="N111" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O111" t="s" s="2">
         <v>255</v>
       </c>
@@ -15747,7 +15774,7 @@
         <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15770,10 +15797,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15866,7 +15893,7 @@
         <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>101</v>
@@ -15889,7 +15916,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>437</v>
@@ -15958,7 +15985,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>78</v>
@@ -16008,7 +16035,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>447</v>
@@ -16123,7 +16150,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>449</v>
@@ -16240,10 +16267,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16359,10 +16386,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16476,10 +16503,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16593,10 +16620,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16710,10 +16737,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16829,10 +16856,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16948,14 +16975,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16974,13 +17001,13 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17031,7 +17058,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>89</v>
@@ -17052,21 +17079,21 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17178,10 +17205,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17295,10 +17322,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17324,13 +17351,13 @@
         <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17380,7 +17407,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17389,7 +17416,7 @@
         <v>89</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>101</v>
@@ -17412,10 +17439,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17441,13 +17468,13 @@
         <v>130</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17476,10 +17503,10 @@
         <v>146</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>78</v>
@@ -17497,7 +17524,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17529,10 +17556,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17558,13 +17585,13 @@
         <v>343</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17614,7 +17641,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17646,10 +17673,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17675,13 +17702,13 @@
         <v>103</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17731,7 +17758,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17763,10 +17790,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17789,16 +17816,16 @@
         <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17848,7 +17875,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17869,21 +17896,21 @@
         <v>78</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17995,10 +18022,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18112,10 +18139,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18141,13 +18168,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18197,7 +18224,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18206,7 +18233,7 @@
         <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>101</v>
@@ -18229,10 +18256,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18258,13 +18285,13 @@
         <v>130</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18293,10 +18320,10 @@
         <v>146</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>78</v>
@@ -18314,7 +18341,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18346,10 +18373,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18375,13 +18402,13 @@
         <v>343</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18431,7 +18458,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18463,10 +18490,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18492,13 +18519,13 @@
         <v>103</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18548,7 +18575,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18580,10 +18607,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18609,13 +18636,13 @@
         <v>208</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18653,17 +18680,17 @@
         <v>78</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18684,24 +18711,24 @@
         <v>78</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>78</v>
@@ -18726,13 +18753,13 @@
         <v>208</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18782,7 +18809,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18800,27 +18827,27 @@
         <v>85</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>78</v>
@@ -18842,16 +18869,16 @@
         <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18901,7 +18928,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18922,21 +18949,21 @@
         <v>78</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18959,13 +18986,13 @@
         <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19016,7 +19043,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19040,7 +19067,7 @@
         <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>78</v>
@@ -19048,10 +19075,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19074,13 +19101,13 @@
         <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19131,7 +19158,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19155,7 +19182,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -19163,10 +19190,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19189,13 +19216,13 @@
         <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19246,7 +19273,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19267,7 +19294,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19278,10 +19305,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19393,10 +19420,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19510,14 +19537,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19539,10 +19566,10 @@
         <v>109</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>112</v>
@@ -19597,7 +19624,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19629,10 +19656,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19658,14 +19685,14 @@
         <v>277</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19693,10 +19720,10 @@
         <v>154</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>78</v>
@@ -19714,7 +19741,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19735,21 +19762,21 @@
         <v>78</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19772,17 +19799,17 @@
         <v>90</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19831,7 +19858,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>89</v>
@@ -19852,21 +19879,21 @@
         <v>78</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19889,17 +19916,17 @@
         <v>78</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -19948,7 +19975,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19980,10 +20007,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20006,17 +20033,17 @@
         <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20065,7 +20092,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20089,7 +20116,7 @@
         <v>78</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>78</v>
@@ -20097,10 +20124,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20126,13 +20153,13 @@
         <v>277</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20161,10 +20188,10 @@
         <v>154</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20182,7 +20209,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20203,10 +20230,10 @@
         <v>78</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20214,10 +20241,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20240,16 +20267,16 @@
         <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20299,7 +20326,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20320,10 +20347,10 @@
         <v>78</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>78</v>
@@ -20331,10 +20358,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20360,13 +20387,13 @@
         <v>277</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20395,10 +20422,10 @@
         <v>154</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>78</v>
@@ -20416,7 +20443,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20443,15 +20470,15 @@
         <v>78</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20563,10 +20590,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20680,12 +20707,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="C154" s="2"/>
+      <c r="C154" t="s" s="2">
+        <v>647</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20694,32 +20723,28 @@
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>142</v>
+        <v>648</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>283</v>
+        <v>649</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20755,17 +20780,19 @@
         <v>78</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AC154" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20777,7 +20804,7 @@
         <v>78</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>78</v>
@@ -20792,19 +20819,17 @@
         <v>78</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>78</v>
       </c>
@@ -20813,7 +20838,7 @@
         <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>90</v>
@@ -20828,10 +20853,10 @@
         <v>142</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>406</v>
+        <v>284</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>285</v>
@@ -20874,16 +20899,14 @@
         <v>78</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="AC155" s="2"/>
       <c r="AD155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF155" t="s" s="2">
         <v>287</v>
@@ -20916,14 +20939,16 @@
         <v>288</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C156" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="D156" t="s" s="2">
         <v>78</v>
       </c>
@@ -20935,25 +20960,29 @@
         <v>89</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>78</v>
       </c>
@@ -21001,19 +21030,19 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>78</v>
@@ -21028,26 +21057,26 @@
         <v>78</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>78</v>
@@ -21059,17 +21088,15 @@
         <v>78</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21106,31 +21133,31 @@
         <v>78</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>78</v>
@@ -21148,48 +21175,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>78</v>
       </c>
@@ -21198,7 +21223,7 @@
         <v>78</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>78</v>
@@ -21225,31 +21250,31 @@
         <v>78</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>78</v>
@@ -21264,15 +21289,15 @@
         <v>78</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21280,7 +21305,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>89</v>
@@ -21295,18 +21320,20 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21315,7 +21342,7 @@
         <v>78</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>78</v>
@@ -21354,7 +21381,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21381,15 +21408,15 @@
         <v>78</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21397,7 +21424,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>89</v>
@@ -21412,18 +21439,18 @@
         <v>90</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>78</v>
       </c>
@@ -21471,7 +21498,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21498,15 +21525,15 @@
         <v>78</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21514,13 +21541,13 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>78</v>
@@ -21529,17 +21556,17 @@
         <v>90</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -21588,7 +21615,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21615,15 +21642,15 @@
         <v>78</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21646,19 +21673,17 @@
         <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
@@ -21707,7 +21732,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21734,15 +21759,15 @@
         <v>78</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21765,19 +21790,19 @@
         <v>90</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>78</v>
@@ -21826,7 +21851,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -21853,15 +21878,15 @@
         <v>78</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21875,7 +21900,7 @@
         <v>89</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>78</v>
@@ -21884,18 +21909,20 @@
         <v>90</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>665</v>
+        <v>307</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>666</v>
+        <v>308</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>78</v>
       </c>
@@ -21919,11 +21946,13 @@
         <v>78</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y164" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z164" t="s" s="2">
-        <v>668</v>
+        <v>78</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>78</v>
@@ -21941,7 +21970,7 @@
         <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>664</v>
+        <v>311</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21959,7 +21988,7 @@
         <v>78</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>669</v>
+        <v>78</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>78</v>
@@ -21968,10 +21997,10 @@
         <v>78</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>670</v>
       </c>
@@ -21990,24 +22019,26 @@
         <v>89</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>104</v>
+        <v>671</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>78</v>
@@ -22032,13 +22063,11 @@
         <v>78</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>78</v>
+        <v>674</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>78</v>
@@ -22056,7 +22085,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>106</v>
+        <v>670</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22068,13 +22097,13 @@
         <v>78</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>78</v>
+        <v>675</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>78</v>
@@ -22088,21 +22117,21 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>78</v>
@@ -22114,17 +22143,15 @@
         <v>78</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -22161,31 +22188,31 @@
         <v>78</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>78</v>
@@ -22205,14 +22232,14 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -22228,23 +22255,21 @@
         <v>78</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>673</v>
+        <v>110</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>674</v>
+        <v>111</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>78</v>
       </c>
@@ -22280,19 +22305,19 @@
         <v>78</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22304,7 +22329,7 @@
         <v>78</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>78</v>
@@ -22319,15 +22344,15 @@
         <v>78</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22338,7 +22363,7 @@
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>78</v>
@@ -22347,19 +22372,23 @@
         <v>78</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>104</v>
+        <v>679</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
       </c>
@@ -22407,19 +22436,19 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>78</v>
@@ -22434,26 +22463,26 @@
         <v>78</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>78</v>
@@ -22465,17 +22494,15 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22512,31 +22539,31 @@
         <v>78</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>78</v>
@@ -22554,48 +22581,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>78</v>
       </c>
@@ -22604,7 +22629,7 @@
         <v>78</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>678</v>
+        <v>78</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>78</v>
@@ -22631,31 +22656,31 @@
         <v>78</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>78</v>
@@ -22670,15 +22695,15 @@
         <v>78</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22692,7 +22717,7 @@
         <v>89</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>78</v>
@@ -22701,18 +22726,20 @@
         <v>90</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P171" t="s" s="2">
         <v>78</v>
       </c>
@@ -22721,7 +22748,7 @@
         <v>78</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>78</v>
+        <v>684</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>78</v>
@@ -22760,7 +22787,7 @@
         <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22787,15 +22814,15 @@
         <v>78</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22809,7 +22836,7 @@
         <v>89</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>78</v>
@@ -22818,18 +22845,18 @@
         <v>90</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>78</v>
       </c>
@@ -22877,7 +22904,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22904,15 +22931,15 @@
         <v>78</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22926,7 +22953,7 @@
         <v>89</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>78</v>
@@ -22935,17 +22962,17 @@
         <v>90</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
@@ -22994,7 +23021,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23021,15 +23048,15 @@
         <v>78</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23052,19 +23079,17 @@
         <v>90</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
@@ -23113,7 +23138,7 @@
         <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23140,15 +23165,15 @@
         <v>78</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23171,19 +23196,19 @@
         <v>90</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>78</v>
@@ -23232,7 +23257,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23259,15 +23284,15 @@
         <v>78</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23278,7 +23303,7 @@
         <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>78</v>
@@ -23287,21 +23312,23 @@
         <v>78</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>685</v>
+        <v>103</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>686</v>
+        <v>307</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>687</v>
+        <v>308</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O176" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>78</v>
       </c>
@@ -23349,13 +23376,13 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>684</v>
+        <v>311</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>78</v>
@@ -23376,15 +23403,15 @@
         <v>78</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23398,7 +23425,7 @@
         <v>80</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>78</v>
@@ -23407,16 +23434,16 @@
         <v>78</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>277</v>
+        <v>691</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23442,29 +23469,31 @@
         <v>78</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>693</v>
+        <v>78</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>694</v>
+        <v>78</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AC177" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23482,28 +23511,26 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="AM177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>696</v>
-      </c>
       <c r="B178" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>697</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>78</v>
       </c>
@@ -23527,13 +23554,13 @@
         <v>277</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23559,29 +23586,29 @@
         <v>78</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y178" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>699</v>
+      </c>
       <c r="Z178" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23599,7 +23626,7 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>78</v>
+        <v>701</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>78</v>
@@ -23611,14 +23638,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23627,10 +23656,10 @@
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>78</v>
@@ -23639,15 +23668,17 @@
         <v>78</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>104</v>
+        <v>696</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N179" s="2"/>
+        <v>697</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23672,13 +23703,11 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>78</v>
+        <v>704</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23696,19 +23725,19 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>106</v>
+        <v>695</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>78</v>
@@ -23728,21 +23757,21 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>78</v>
@@ -23754,17 +23783,15 @@
         <v>78</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -23801,31 +23828,31 @@
         <v>78</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>78</v>
@@ -23845,14 +23872,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -23868,23 +23895,21 @@
         <v>78</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>705</v>
+        <v>110</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>706</v>
+        <v>111</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>78</v>
       </c>
@@ -23920,19 +23945,19 @@
         <v>78</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -23944,7 +23969,7 @@
         <v>78</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>78</v>
@@ -23959,15 +23984,15 @@
         <v>78</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23978,7 +24003,7 @@
         <v>79</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>78</v>
@@ -23987,19 +24012,23 @@
         <v>78</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>104</v>
+        <v>711</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>712</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>78</v>
       </c>
@@ -24047,19 +24076,19 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>78</v>
@@ -24074,26 +24103,26 @@
         <v>78</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>78</v>
@@ -24105,17 +24134,15 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>78</v>
@@ -24152,31 +24179,31 @@
         <v>78</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>78</v>
@@ -24196,21 +24223,21 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>78</v>
@@ -24219,23 +24246,21 @@
         <v>78</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24244,7 +24269,7 @@
         <v>78</v>
       </c>
       <c r="S184" t="s" s="2">
-        <v>713</v>
+        <v>78</v>
       </c>
       <c r="T184" t="s" s="2">
         <v>78</v>
@@ -24271,31 +24296,31 @@
         <v>78</v>
       </c>
       <c r="AB184" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC184" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE184" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>78</v>
@@ -24310,15 +24335,15 @@
         <v>78</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24341,18 +24366,20 @@
         <v>90</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>78</v>
       </c>
@@ -24361,7 +24388,7 @@
         <v>78</v>
       </c>
       <c r="S185" t="s" s="2">
-        <v>78</v>
+        <v>719</v>
       </c>
       <c r="T185" t="s" s="2">
         <v>78</v>
@@ -24400,7 +24427,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -24427,15 +24454,15 @@
         <v>78</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24443,13 +24470,13 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>78</v>
@@ -24458,18 +24485,18 @@
         <v>90</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>78</v>
       </c>
@@ -24517,7 +24544,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24544,15 +24571,15 @@
         <v>78</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24560,13 +24587,13 @@
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G187" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>78</v>
@@ -24575,17 +24602,17 @@
         <v>90</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24634,7 +24661,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24661,15 +24688,15 @@
         <v>78</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24692,19 +24719,17 @@
         <v>90</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24753,7 +24778,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24780,15 +24805,15 @@
         <v>78</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24811,19 +24836,19 @@
         <v>90</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -24872,7 +24897,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -24899,19 +24924,17 @@
         <v>78</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>725</v>
-      </c>
+        <v>729</v>
+      </c>
+      <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
         <v>78</v>
       </c>
@@ -24920,30 +24943,32 @@
         <v>79</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J190" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I190" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K190" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>690</v>
+        <v>307</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>691</v>
+        <v>308</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O190" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>78</v>
       </c>
@@ -24967,11 +24992,13 @@
         <v>78</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y190" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z190" t="s" s="2">
-        <v>726</v>
+        <v>78</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>78</v>
@@ -24989,13 +25016,13 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>689</v>
+        <v>311</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>78</v>
@@ -25016,17 +25043,19 @@
         <v>78</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C191" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="D191" t="s" s="2">
         <v>78</v>
       </c>
@@ -25035,10 +25064,10 @@
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>78</v>
@@ -25047,15 +25076,17 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>104</v>
+        <v>696</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N191" s="2"/>
+        <v>697</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -25080,13 +25111,11 @@
         <v>78</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>78</v>
+        <v>732</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>78</v>
@@ -25104,19 +25133,19 @@
         <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>106</v>
+        <v>695</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>78</v>
@@ -25136,21 +25165,21 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>78</v>
@@ -25162,17 +25191,15 @@
         <v>78</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>78</v>
@@ -25209,31 +25236,31 @@
         <v>78</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>78</v>
@@ -25253,14 +25280,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -25276,23 +25303,21 @@
         <v>78</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>730</v>
+        <v>110</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>731</v>
+        <v>111</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>78</v>
       </c>
@@ -25328,19 +25353,19 @@
         <v>78</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -25352,7 +25377,7 @@
         <v>78</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>78</v>
@@ -25367,15 +25392,15 @@
         <v>78</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25386,7 +25411,7 @@
         <v>79</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>78</v>
@@ -25395,19 +25420,23 @@
         <v>78</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>104</v>
+        <v>736</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>737</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25455,19 +25484,19 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>78</v>
@@ -25482,26 +25511,26 @@
         <v>78</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>78</v>
@@ -25513,17 +25542,15 @@
         <v>78</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>78</v>
@@ -25560,31 +25587,31 @@
         <v>78</v>
       </c>
       <c r="AB195" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC195" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE195" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>78</v>
@@ -25604,21 +25631,21 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>78</v>
@@ -25627,23 +25654,21 @@
         <v>78</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>78</v>
       </c>
@@ -25652,7 +25677,7 @@
         <v>78</v>
       </c>
       <c r="S196" t="s" s="2">
-        <v>735</v>
+        <v>78</v>
       </c>
       <c r="T196" t="s" s="2">
         <v>78</v>
@@ -25679,31 +25704,31 @@
         <v>78</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC196" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>78</v>
@@ -25718,15 +25743,15 @@
         <v>78</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25734,7 +25759,7 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G197" t="s" s="2">
         <v>89</v>
@@ -25749,18 +25774,20 @@
         <v>90</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O197" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P197" t="s" s="2">
         <v>78</v>
       </c>
@@ -25769,7 +25796,7 @@
         <v>78</v>
       </c>
       <c r="S197" t="s" s="2">
-        <v>78</v>
+        <v>741</v>
       </c>
       <c r="T197" t="s" s="2">
         <v>78</v>
@@ -25808,7 +25835,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25835,15 +25862,15 @@
         <v>78</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25851,7 +25878,7 @@
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>89</v>
@@ -25866,18 +25893,18 @@
         <v>90</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>78</v>
       </c>
@@ -25925,7 +25952,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -25952,15 +25979,15 @@
         <v>78</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25968,7 +25995,7 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G199" t="s" s="2">
         <v>89</v>
@@ -25983,17 +26010,17 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -26042,7 +26069,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26069,15 +26096,15 @@
         <v>78</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26100,19 +26127,17 @@
         <v>90</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26161,7 +26186,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26188,15 +26213,15 @@
         <v>78</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26219,19 +26244,19 @@
         <v>90</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26280,7 +26305,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26307,15 +26332,15 @@
         <v>78</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26326,7 +26351,7 @@
         <v>79</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H202" t="s" s="2">
         <v>78</v>
@@ -26335,20 +26360,22 @@
         <v>78</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>742</v>
+        <v>103</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>743</v>
+        <v>307</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>745</v>
+        <v>310</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26397,13 +26424,13 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>741</v>
+        <v>311</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>78</v>
@@ -26424,15 +26451,15 @@
         <v>78</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26455,16 +26482,18 @@
         <v>78</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>277</v>
+        <v>748</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="N203" s="2"/>
-      <c r="O203" s="2"/>
+      <c r="O203" t="s" s="2">
+        <v>751</v>
+      </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
       </c>
@@ -26488,13 +26517,13 @@
         <v>78</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>749</v>
+        <v>78</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>750</v>
+        <v>78</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>78</v>
@@ -26512,7 +26541,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26542,12 +26571,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26561,7 +26590,7 @@
         <v>80</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>78</v>
@@ -26570,7 +26599,7 @@
         <v>78</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>752</v>
+        <v>277</v>
       </c>
       <c r="L204" t="s" s="2">
         <v>753</v>
@@ -26603,13 +26632,13 @@
         <v>78</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>78</v>
+        <v>755</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>78</v>
+        <v>756</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>78</v>
@@ -26627,7 +26656,7 @@
         <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -26648,16 +26677,16 @@
         <v>78</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>755</v>
+        <v>78</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>756</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="205" hidden="true">
+    <row r="205">
       <c r="A205" t="s" s="2">
         <v>757</v>
       </c>
@@ -26676,7 +26705,7 @@
         <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>78</v>
@@ -26685,13 +26714,13 @@
         <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>584</v>
+        <v>758</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -26763,21 +26792,21 @@
         <v>78</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>78</v>
+        <v>761</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>78</v>
+        <v>762</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26788,7 +26817,7 @@
         <v>79</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>78</v>
@@ -26800,13 +26829,13 @@
         <v>78</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>103</v>
+        <v>585</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>104</v>
+        <v>764</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>105</v>
+        <v>765</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -26857,19 +26886,19 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>106</v>
+        <v>763</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>78</v>
@@ -26889,21 +26918,21 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>78</v>
@@ -26915,17 +26944,15 @@
         <v>78</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>78</v>
@@ -26974,19 +27001,19 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>78</v>
@@ -27006,14 +27033,14 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>591</v>
+        <v>108</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
@@ -27026,26 +27053,24 @@
         <v>78</v>
       </c>
       <c r="I208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>592</v>
+        <v>110</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>593</v>
+        <v>111</v>
       </c>
       <c r="N208" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O208" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>78</v>
       </c>
@@ -27093,7 +27118,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>594</v>
+        <v>116</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27125,42 +27150,46 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>764</v>
+        <v>593</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="N209" s="2"/>
-      <c r="O209" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>78</v>
       </c>
@@ -27184,13 +27213,13 @@
         <v>78</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>766</v>
+        <v>78</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>767</v>
+        <v>78</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27208,19 +27237,19 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>763</v>
+        <v>595</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>78</v>
@@ -27240,10 +27269,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27251,7 +27280,7 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G210" t="s" s="2">
         <v>89</v>
@@ -27266,7 +27295,7 @@
         <v>78</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>769</v>
+        <v>277</v>
       </c>
       <c r="L210" t="s" s="2">
         <v>770</v>
@@ -27299,13 +27328,13 @@
         <v>78</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>78</v>
+        <v>772</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>78</v>
+        <v>773</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>78</v>
@@ -27323,10 +27352,10 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>89</v>
@@ -27355,10 +27384,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27366,10 +27395,10 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>78</v>
@@ -27381,20 +27410,16 @@
         <v>78</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O211" t="s" s="2">
         <v>777</v>
       </c>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>78</v>
       </c>
@@ -27442,13 +27467,13 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>78</v>
@@ -27500,18 +27525,20 @@
         <v>78</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>277</v>
+        <v>779</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O212" s="2"/>
+        <v>782</v>
+      </c>
+      <c r="O212" t="s" s="2">
+        <v>783</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
       </c>
@@ -27535,13 +27562,13 @@
         <v>78</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>781</v>
+        <v>78</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>782</v>
+        <v>78</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>78</v>
@@ -27589,8 +27616,125 @@
         <v>78</v>
       </c>
     </row>
+    <row r="213" hidden="true">
+      <c r="A213" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="C213" s="2"/>
+      <c r="D213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E213" s="2"/>
+      <c r="F213" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G213" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K213" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L213" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M213" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="O213" s="2"/>
+      <c r="P213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q213" s="2"/>
+      <c r="R213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X213" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y213" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="Z213" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AA213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF213" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AG213" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH213" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ213" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO213" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO212">
+  <autoFilter ref="A1:AO213">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27600,7 +27744,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI211">
+  <conditionalFormatting sqref="A2:AI212">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-mamma-sozialdienst.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
